--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.5516773992661</v>
+        <v>12.11464757738074</v>
       </c>
       <c r="D2" t="n">
-        <v>60.00648355166029</v>
+        <v>9.751053577144797</v>
       </c>
       <c r="E2" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F2" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.30023717258877</v>
+        <v>9.798788540545674</v>
       </c>
       <c r="D3" t="n">
-        <v>27.85437058263592</v>
+        <v>4.526335219678337</v>
       </c>
       <c r="E3" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F3" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.59535417018749</v>
+        <v>9.684245052655468</v>
       </c>
       <c r="D4" t="n">
-        <v>40.55814619534098</v>
+        <v>6.59069875674291</v>
       </c>
       <c r="E4" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F4" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>73.89338805039179</v>
+        <v>12.00767555818867</v>
       </c>
       <c r="D5" t="n">
-        <v>70.33853654612557</v>
+        <v>11.4300121887454</v>
       </c>
       <c r="E5" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F5" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.34778819917634</v>
+        <v>8.831515582366155</v>
       </c>
       <c r="D6" t="n">
-        <v>17.70009744168185</v>
+        <v>2.876265834273301</v>
       </c>
       <c r="E6" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F6" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.13456857288962</v>
+        <v>7.496867393094563</v>
       </c>
       <c r="D7" t="n">
-        <v>44.71213793276172</v>
+        <v>7.26572241407378</v>
       </c>
       <c r="E7" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F7" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.87431703827235</v>
+        <v>6.967076518719257</v>
       </c>
       <c r="D8" t="n">
-        <v>43.21338445864878</v>
+        <v>7.022174974530428</v>
       </c>
       <c r="E8" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F8" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.25308919033317</v>
+        <v>5.403626993429141</v>
       </c>
       <c r="D9" t="n">
-        <v>33.42372016636302</v>
+        <v>5.43135452703399</v>
       </c>
       <c r="E9" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F9" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.70692086696747</v>
+        <v>8.077374640882214</v>
       </c>
       <c r="D10" t="n">
-        <v>49.51206919894435</v>
+        <v>8.045711244828457</v>
       </c>
       <c r="E10" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F10" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.97023783048568</v>
+        <v>7.632663647453923</v>
       </c>
       <c r="D11" t="n">
-        <v>46.62461533604407</v>
+        <v>7.576499992107161</v>
       </c>
       <c r="E11" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F11" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.32470594877626</v>
+        <v>6.552764716676141</v>
       </c>
       <c r="D12" t="n">
-        <v>39.83166681769937</v>
+        <v>6.472645857876148</v>
       </c>
       <c r="E12" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F12" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.04754509442928</v>
+        <v>4.557726077844759</v>
       </c>
       <c r="D13" t="n">
-        <v>27.06718531535271</v>
+        <v>4.398417613744816</v>
       </c>
       <c r="E13" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F13" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.23919887068082</v>
+        <v>5.238869816485633</v>
       </c>
       <c r="D14" t="n">
-        <v>31.60331678608034</v>
+        <v>5.135538977738055</v>
       </c>
       <c r="E14" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F14" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.21818495824355</v>
+        <v>5.235455055714577</v>
       </c>
       <c r="D15" t="n">
-        <v>31.23966076013632</v>
+        <v>5.076444873522153</v>
       </c>
       <c r="E15" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F15" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.33556788822965</v>
+        <v>7.042029781837319</v>
       </c>
       <c r="D16" t="n">
-        <v>43.82902418659401</v>
+        <v>7.122216430321527</v>
       </c>
       <c r="E16" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F16" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.62428516564578</v>
+        <v>6.926446339417439</v>
       </c>
       <c r="D17" t="n">
-        <v>41.75208553413432</v>
+        <v>6.784713899296828</v>
       </c>
       <c r="E17" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F17" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.53321085058517</v>
+        <v>3.011646763220091</v>
       </c>
       <c r="D18" t="n">
-        <v>18.97938589522045</v>
+        <v>3.084150207973323</v>
       </c>
       <c r="E18" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F18" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9.915729181868508</v>
+        <v>1.611305992053633</v>
       </c>
       <c r="D19" t="n">
-        <v>9.940964494230796</v>
+        <v>1.615406730312504</v>
       </c>
       <c r="E19" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F19" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>29.81897048557963</v>
+        <v>4.845582703906691</v>
       </c>
       <c r="D20" t="n">
-        <v>30.35492639873475</v>
+        <v>4.932675539794397</v>
       </c>
       <c r="E20" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F20" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>5.490049993678922</v>
+        <v>0.8921331239728248</v>
       </c>
       <c r="D21" t="n">
-        <v>6.02535145554585</v>
+        <v>0.9791196115262006</v>
       </c>
       <c r="E21" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F21" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>62.15322918130689</v>
+        <v>10.09989974196237</v>
       </c>
       <c r="D22" t="n">
-        <v>62.66363295936335</v>
+        <v>10.18284035589654</v>
       </c>
       <c r="E22" t="n">
-        <v>18.13907085049184</v>
+        <v>2.947599013204925</v>
       </c>
       <c r="F22" t="n">
-        <v>16.07563317093875</v>
+        <v>2.612290390277547</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
